--- a/RFQ.xlx.xlsx
+++ b/RFQ.xlx.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="18945" windowHeight="7500"/>
+    <workbookView windowWidth="19185" windowHeight="7500"/>
   </bookViews>
   <sheets>
     <sheet name="RFQ Template" sheetId="1" r:id="rId1"/>
@@ -264,7 +264,7 @@
     <numFmt numFmtId="178" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="179" formatCode="_ &quot;₹&quot;* #,##0_ ;_ &quot;₹&quot;* \-#,##0_ ;_ &quot;₹&quot;* &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -280,6 +280,7 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <i/>
       <sz val="10"/>
       <color rgb="FF333333"/>
@@ -287,6 +288,7 @@
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="10"/>
       <color theme="1"/>
       <name val="Microsoft YaHei"/>
@@ -296,6 +298,12 @@
       <b/>
       <sz val="10"/>
       <color rgb="FFFFFFFF"/>
+      <name val="Microsoft YaHei"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
       <name val="Microsoft YaHei"/>
       <charset val="134"/>
     </font>
@@ -462,18 +470,18 @@
     </font>
     <font>
       <b/>
+      <sz val="10"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <name val="Calibri"/>
       <charset val="134"/>
     </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-    </font>
   </fonts>
-  <fills count="37">
+  <fills count="41">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -482,7 +490,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FF1F4E78"/>
+        <fgColor theme="3" tint="0.4"/>
         <bgColor rgb="FF1F4E78"/>
       </patternFill>
     </fill>
@@ -494,14 +502,38 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="3" tint="0.4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.15"/>
+        <bgColor rgb="FFD9E1F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FFFFF2CC"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF5ACE86"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFD9E1F2"/>
         <bgColor rgb="FFD9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FFFFF2CC"/>
+        <fgColor theme="5" tint="0.4"/>
+        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -1029,137 +1061,137 @@
     <xf numFmtId="179" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="17" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="8" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="9" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="18" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="19" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="11" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="21" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="20" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="22" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="23" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="24" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="25" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="47">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1182,109 +1214,121 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="6" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1340,6 +1384,13 @@
     <cellStyle name="60% - Accent6" xfId="48" builtinId="52"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <mruColors>
+      <color rgb="00B83ECE"/>
+      <color rgb="005ACE86"/>
+      <color rgb="008E4AC3"/>
+    </mruColors>
+  </colors>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
@@ -1633,17 +1684,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H35"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="18.4285714285714" customWidth="1"/>
-    <col min="2" max="2" width="31.2095238095238" customWidth="1"/>
-    <col min="3" max="3" width="15" customWidth="1"/>
-    <col min="4" max="4" width="10.7142857142857" customWidth="1"/>
-    <col min="5" max="5" width="28.1428571428571" customWidth="1"/>
-    <col min="6" max="6" width="22.3333333333333" customWidth="1"/>
-    <col min="7" max="7" width="16.7142857142857" customWidth="1"/>
-    <col min="8" max="8" width="23.2857142857143" customWidth="1"/>
+    <col min="1" max="1" width="21.952380952381" customWidth="1"/>
+    <col min="2" max="2" width="24.0952380952381" customWidth="1"/>
+    <col min="3" max="3" width="19.7142857142857" customWidth="1"/>
+    <col min="4" max="4" width="12.4571428571429" customWidth="1"/>
+    <col min="5" max="5" width="26.9047619047619" customWidth="1"/>
+    <col min="6" max="6" width="27" customWidth="1"/>
+    <col min="7" max="7" width="22.7142857142857" customWidth="1"/>
+    <col min="8" max="8" width="29.7142857142857" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="24.5" customHeight="1" spans="1:8">
@@ -1674,163 +1725,163 @@
       <c r="A3" s="7" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="5"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="5"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="6"/>
+      <c r="B3" s="8"/>
+      <c r="C3" s="8"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
+      <c r="F3" s="8"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="9"/>
     </row>
     <row r="4" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A4" s="8" t="s">
+      <c r="A4" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="9"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="11"/>
-      <c r="E4" s="12" t="s">
+      <c r="B4" s="11"/>
+      <c r="C4" s="12"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="14" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="13" t="s">
+      <c r="F4" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="14"/>
-      <c r="H4" s="15"/>
+      <c r="G4" s="16"/>
+      <c r="H4" s="17"/>
     </row>
     <row r="5" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A5" s="8" t="s">
+      <c r="A5" s="10" t="s">
         <v>6</v>
       </c>
-      <c r="B5" s="9"/>
-      <c r="C5" s="10"/>
-      <c r="D5" s="11"/>
-      <c r="E5" s="12" t="s">
+      <c r="B5" s="11"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="13"/>
+      <c r="E5" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="F5" s="13"/>
-      <c r="G5" s="14"/>
-      <c r="H5" s="15"/>
+      <c r="F5" s="15"/>
+      <c r="G5" s="16"/>
+      <c r="H5" s="17"/>
     </row>
     <row r="6" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A6" s="8" t="s">
+      <c r="A6" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="12" t="s">
+      <c r="B6" s="11"/>
+      <c r="C6" s="12"/>
+      <c r="D6" s="13"/>
+      <c r="E6" s="14" t="s">
         <v>9</v>
       </c>
-      <c r="F6" s="13" t="s">
+      <c r="F6" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G6" s="14"/>
-      <c r="H6" s="15"/>
+      <c r="G6" s="16"/>
+      <c r="H6" s="17"/>
     </row>
     <row r="7" ht="35" customHeight="1" spans="1:8">
-      <c r="A7" s="8" t="s">
+      <c r="A7" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="11" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="11"/>
-      <c r="E7" s="12" t="s">
+      <c r="C7" s="18"/>
+      <c r="D7" s="19"/>
+      <c r="E7" s="14" t="s">
         <v>12</v>
       </c>
-      <c r="F7" s="13" t="s">
+      <c r="F7" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G7" s="14"/>
-      <c r="H7" s="15"/>
-    </row>
-    <row r="8" ht="35" customHeight="1" spans="1:8">
-      <c r="A8" s="8" t="s">
+      <c r="G7" s="16"/>
+      <c r="H7" s="17"/>
+    </row>
+    <row r="8" ht="18.5" customHeight="1" spans="1:8">
+      <c r="A8" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="16" t="s">
+      <c r="B8" s="11" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="11"/>
-      <c r="E8" s="12" t="s">
+      <c r="C8" s="12"/>
+      <c r="D8" s="13"/>
+      <c r="E8" s="14" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="13" t="s">
+      <c r="F8" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G8" s="14"/>
-      <c r="H8" s="15"/>
-    </row>
-    <row r="9" ht="35" customHeight="1" spans="1:8">
-      <c r="A9" s="8" t="s">
+      <c r="G8" s="16"/>
+      <c r="H8" s="17"/>
+    </row>
+    <row r="9" ht="18.5" customHeight="1" spans="1:8">
+      <c r="A9" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="B9" s="16"/>
-      <c r="C9" s="10"/>
-      <c r="D9" s="11"/>
-      <c r="E9" s="12" t="s">
+      <c r="B9" s="11"/>
+      <c r="C9" s="12"/>
+      <c r="D9" s="13"/>
+      <c r="E9" s="14" t="s">
         <v>17</v>
       </c>
-      <c r="F9" s="13"/>
-      <c r="G9" s="14"/>
-      <c r="H9" s="15"/>
-    </row>
-    <row r="10" ht="35" customHeight="1" spans="1:8">
-      <c r="A10" s="8" t="s">
+      <c r="F9" s="15"/>
+      <c r="G9" s="16"/>
+      <c r="H9" s="17"/>
+    </row>
+    <row r="10" ht="18.5" customHeight="1" spans="1:8">
+      <c r="A10" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="17"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="19"/>
+      <c r="B10" s="11"/>
+      <c r="C10" s="12"/>
+      <c r="D10" s="12"/>
+      <c r="E10" s="12"/>
+      <c r="F10" s="12"/>
+      <c r="G10" s="12"/>
+      <c r="H10" s="20"/>
     </row>
     <row r="11" ht="18.5" customHeight="1" spans="1:8">
       <c r="A11" s="7" t="s">
         <v>19</v>
       </c>
-      <c r="B11" s="5"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="5"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="5"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="6"/>
+      <c r="B11" s="8"/>
+      <c r="C11" s="8"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
+      <c r="F11" s="8"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="9"/>
     </row>
     <row r="12" ht="35" customHeight="1" spans="1:8">
-      <c r="A12" s="20" t="s">
+      <c r="A12" s="21" t="s">
         <v>20</v>
       </c>
-      <c r="B12" s="21" t="s">
+      <c r="B12" s="22" t="s">
         <v>21</v>
       </c>
-      <c r="C12" s="21"/>
-      <c r="D12" s="21" t="s">
+      <c r="C12" s="22"/>
+      <c r="D12" s="22" t="s">
         <v>22</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E12" s="22" t="s">
         <v>23</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="F12" s="22" t="s">
         <v>24</v>
       </c>
-      <c r="G12" s="21" t="s">
+      <c r="G12" s="22" t="s">
         <v>25</v>
       </c>
-      <c r="H12" s="22" t="s">
+      <c r="H12" s="23" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="13" ht="32" customHeight="1" spans="1:8">
-      <c r="A13" s="23">
+    <row r="13" ht="18.5" customHeight="1" spans="1:8">
+      <c r="A13" s="24">
         <v>1</v>
       </c>
-      <c r="B13" s="24"/>
+      <c r="B13" s="25"/>
       <c r="C13" s="25"/>
       <c r="D13" s="25"/>
       <c r="E13" s="25"/>
@@ -1839,12 +1890,12 @@
         <v>5</v>
       </c>
       <c r="H13" s="27" t="e">
-        <f>D13*G13</f>
+        <f>G13*D13</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="14" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A14" s="23">
+      <c r="A14" s="24">
         <v>2</v>
       </c>
       <c r="B14" s="25"/>
@@ -1856,12 +1907,12 @@
         <v>5</v>
       </c>
       <c r="H14" s="27" t="e">
-        <f>D14*G14</f>
+        <f>G14*D14</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="15" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A15" s="23">
+      <c r="A15" s="24">
         <v>3</v>
       </c>
       <c r="B15" s="25"/>
@@ -1873,299 +1924,329 @@
         <v>5</v>
       </c>
       <c r="H15" s="27" t="e">
-        <f>D15*G15</f>
+        <f>G15*D15</f>
         <v>#VALUE!</v>
       </c>
     </row>
     <row r="16" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A16" s="28" t="s">
+      <c r="A16" s="24">
+        <v>4</v>
+      </c>
+      <c r="B16" s="25"/>
+      <c r="C16" s="25"/>
+      <c r="D16" s="25"/>
+      <c r="E16" s="25"/>
+      <c r="F16" s="26"/>
+      <c r="G16" s="26"/>
+      <c r="H16" s="27">
+        <f>G16*D16</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" ht="18.5" customHeight="1" spans="1:8">
+      <c r="A17" s="24">
+        <v>5</v>
+      </c>
+      <c r="B17" s="25"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="25"/>
+      <c r="E17" s="25"/>
+      <c r="F17" s="26"/>
+      <c r="G17" s="26"/>
+      <c r="H17" s="27">
+        <f>G17*D17</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" ht="18.5" customHeight="1" spans="1:8">
+      <c r="A18" s="28" t="s">
         <v>27</v>
       </c>
-      <c r="B16" s="5"/>
-      <c r="C16" s="5"/>
-      <c r="D16" s="5"/>
-      <c r="E16" s="5"/>
-      <c r="F16" s="5"/>
-      <c r="G16" s="5"/>
-      <c r="H16" s="29" t="e">
-        <f>SUM(H13:H15)</f>
+      <c r="B18" s="29"/>
+      <c r="C18" s="29"/>
+      <c r="D18" s="29"/>
+      <c r="E18" s="29"/>
+      <c r="F18" s="29"/>
+      <c r="G18" s="29"/>
+      <c r="H18" s="30" t="e">
+        <f>SUM(H13:H17)</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="17" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A17" s="7" t="s">
+    <row r="19" ht="18.5" customHeight="1" spans="1:8">
+      <c r="A19" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="B17" s="5"/>
-      <c r="C17" s="5"/>
-      <c r="D17" s="5"/>
-      <c r="E17" s="5"/>
-      <c r="F17" s="5"/>
-      <c r="G17" s="5"/>
-      <c r="H17" s="6"/>
-    </row>
-    <row r="18" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A18" s="30" t="s">
+      <c r="B19" s="8"/>
+      <c r="C19" s="8"/>
+      <c r="D19" s="8"/>
+      <c r="E19" s="8"/>
+      <c r="F19" s="8"/>
+      <c r="G19" s="8"/>
+      <c r="H19" s="9"/>
+    </row>
+    <row r="20" ht="18.5" customHeight="1" spans="1:8">
+      <c r="A20" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B20" s="32" t="s">
         <v>30</v>
       </c>
-      <c r="C18" s="31"/>
-      <c r="D18" s="31"/>
-      <c r="E18" s="31" t="s">
+      <c r="C20" s="32"/>
+      <c r="D20" s="32"/>
+      <c r="E20" s="32" t="s">
         <v>31</v>
       </c>
-      <c r="F18" s="31"/>
-      <c r="G18" s="31"/>
-      <c r="H18" s="32" t="s">
+      <c r="F20" s="32"/>
+      <c r="G20" s="32"/>
+      <c r="H20" s="33" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="19" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A19" s="33">
+    <row r="21" ht="18.5" customHeight="1" spans="1:8">
+      <c r="A21" s="34">
         <v>1</v>
       </c>
-      <c r="B19" s="34" t="s">
+      <c r="B21" s="35" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="5"/>
-      <c r="D19" s="5"/>
-      <c r="E19" s="26"/>
-      <c r="F19" s="5"/>
-      <c r="G19" s="5"/>
-      <c r="H19" s="27" t="e">
-        <f>H16</f>
+      <c r="C21" s="36"/>
+      <c r="D21" s="36"/>
+      <c r="E21" s="26"/>
+      <c r="F21" s="36"/>
+      <c r="G21" s="36"/>
+      <c r="H21" s="27" t="e">
+        <f>H18</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="20" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A20" s="33">
+    <row r="22" ht="18.5" customHeight="1" spans="1:8">
+      <c r="A22" s="34">
         <v>2</v>
       </c>
-      <c r="B20" s="34" t="s">
+      <c r="B22" s="35" t="s">
         <v>34</v>
       </c>
-      <c r="C20" s="5"/>
-      <c r="D20" s="5"/>
-      <c r="E20" s="26"/>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5"/>
-      <c r="H20" s="27" t="e">
-        <f>H16</f>
+      <c r="C22" s="36"/>
+      <c r="D22" s="36"/>
+      <c r="E22" s="26"/>
+      <c r="F22" s="36"/>
+      <c r="G22" s="36"/>
+      <c r="H22" s="27">
+        <f>E22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" ht="18.5" customHeight="1" spans="1:8">
+      <c r="A23" s="34">
+        <v>3</v>
+      </c>
+      <c r="B23" s="35" t="s">
+        <v>35</v>
+      </c>
+      <c r="C23" s="36"/>
+      <c r="D23" s="36"/>
+      <c r="E23" s="26"/>
+      <c r="F23" s="36"/>
+      <c r="G23" s="36"/>
+      <c r="H23" s="27" t="e">
+        <f>(H21+H22)*0.18</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="21" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A21" s="33">
-        <v>3</v>
-      </c>
-      <c r="B21" s="34" t="s">
-        <v>35</v>
-      </c>
-      <c r="C21" s="5"/>
-      <c r="D21" s="5"/>
-      <c r="E21" s="26"/>
-      <c r="F21" s="5"/>
-      <c r="G21" s="5"/>
-      <c r="H21" s="27" t="e">
-        <f>H16</f>
+    <row r="24" ht="18.5" customHeight="1" spans="1:8">
+      <c r="A24" s="34">
+        <v>4</v>
+      </c>
+      <c r="B24" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="C24" s="36"/>
+      <c r="D24" s="36"/>
+      <c r="E24" s="26"/>
+      <c r="F24" s="36"/>
+      <c r="G24" s="36"/>
+      <c r="H24" s="27" t="e">
+        <f>H21+H22+H23</f>
         <v>#VALUE!</v>
       </c>
     </row>
-    <row r="22" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A22" s="33">
-        <v>4</v>
-      </c>
-      <c r="B22" s="34" t="s">
-        <v>36</v>
-      </c>
-      <c r="C22" s="5"/>
-      <c r="D22" s="5"/>
-      <c r="E22" s="26"/>
-      <c r="F22" s="5"/>
-      <c r="G22" s="5"/>
-      <c r="H22" s="27" t="e">
-        <f>H16</f>
-        <v>#VALUE!</v>
-      </c>
-    </row>
-    <row r="23" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A23" s="33">
+    <row r="25" ht="18.5" customHeight="1" spans="1:8">
+      <c r="A25" s="34">
         <v>5</v>
       </c>
-      <c r="B23" s="34" t="s">
+      <c r="B25" s="35" t="s">
         <v>37</v>
       </c>
-      <c r="C23" s="5"/>
-      <c r="D23" s="5"/>
-      <c r="E23" s="26"/>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5"/>
-      <c r="H23" s="27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="24" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A24" s="33">
-        <v>6</v>
-      </c>
-      <c r="B24" s="34" t="s">
-        <v>39</v>
-      </c>
-      <c r="C24" s="5"/>
-      <c r="D24" s="5"/>
-      <c r="E24" s="26"/>
-      <c r="F24" s="5"/>
-      <c r="G24" s="5"/>
-      <c r="H24" s="27" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="25" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A25" s="33">
-        <v>7</v>
-      </c>
-      <c r="B25" s="34" t="s">
-        <v>40</v>
-      </c>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
+      <c r="C25" s="36"/>
+      <c r="D25" s="36"/>
       <c r="E25" s="26"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
+      <c r="F25" s="36"/>
+      <c r="G25" s="36"/>
       <c r="H25" s="27" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="26" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A26" s="33">
-        <v>8</v>
-      </c>
-      <c r="B26" s="34" t="s">
-        <v>41</v>
-      </c>
-      <c r="C26" s="5"/>
-      <c r="D26" s="5"/>
+      <c r="A26" s="34">
+        <v>6</v>
+      </c>
+      <c r="B26" s="35" t="s">
+        <v>39</v>
+      </c>
+      <c r="C26" s="36"/>
+      <c r="D26" s="36"/>
       <c r="E26" s="26"/>
-      <c r="F26" s="5"/>
-      <c r="G26" s="5"/>
+      <c r="F26" s="36"/>
+      <c r="G26" s="36"/>
       <c r="H26" s="27" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="27" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A27" s="33">
-        <v>9</v>
-      </c>
-      <c r="B27" s="34" t="s">
-        <v>42</v>
-      </c>
-      <c r="C27" s="5"/>
-      <c r="D27" s="5"/>
+      <c r="A27" s="34">
+        <v>7</v>
+      </c>
+      <c r="B27" s="35" t="s">
+        <v>40</v>
+      </c>
+      <c r="C27" s="36"/>
+      <c r="D27" s="36"/>
       <c r="E27" s="26"/>
-      <c r="F27" s="5"/>
-      <c r="G27" s="5"/>
+      <c r="F27" s="36"/>
+      <c r="G27" s="36"/>
       <c r="H27" s="27" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="28" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A28" s="33">
-        <v>10</v>
-      </c>
-      <c r="B28" s="34" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="5"/>
-      <c r="D28" s="5"/>
+    <row r="28" ht="25" customHeight="1" spans="1:8">
+      <c r="A28" s="34">
+        <v>8</v>
+      </c>
+      <c r="B28" s="35" t="s">
+        <v>41</v>
+      </c>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
       <c r="E28" s="26"/>
-      <c r="F28" s="5"/>
-      <c r="G28" s="5"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
       <c r="H28" s="27" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="29" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A29" s="33">
-        <v>11</v>
-      </c>
-      <c r="B29" s="34" t="s">
-        <v>44</v>
-      </c>
-      <c r="C29" s="5"/>
-      <c r="D29" s="5"/>
+      <c r="A29" s="34">
+        <v>9</v>
+      </c>
+      <c r="B29" s="35" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="36"/>
+      <c r="D29" s="36"/>
       <c r="E29" s="26"/>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5"/>
+      <c r="F29" s="36"/>
+      <c r="G29" s="36"/>
       <c r="H29" s="27" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="30" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A30" s="33">
-        <v>12</v>
-      </c>
-      <c r="B30" s="34" t="s">
-        <v>45</v>
-      </c>
-      <c r="C30" s="5"/>
-      <c r="D30" s="5"/>
+      <c r="A30" s="34">
+        <v>10</v>
+      </c>
+      <c r="B30" s="35" t="s">
+        <v>43</v>
+      </c>
+      <c r="C30" s="36"/>
+      <c r="D30" s="36"/>
       <c r="E30" s="26"/>
-      <c r="F30" s="5"/>
-      <c r="G30" s="5"/>
+      <c r="F30" s="36"/>
+      <c r="G30" s="36"/>
       <c r="H30" s="27" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="31" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A31" s="33">
-        <v>13</v>
-      </c>
-      <c r="B31" s="34" t="s">
-        <v>46</v>
-      </c>
-      <c r="C31" s="5"/>
-      <c r="D31" s="5"/>
+      <c r="A31" s="34">
+        <v>11</v>
+      </c>
+      <c r="B31" s="35" t="s">
+        <v>44</v>
+      </c>
+      <c r="C31" s="36"/>
+      <c r="D31" s="36"/>
       <c r="E31" s="26"/>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5"/>
+      <c r="F31" s="36"/>
+      <c r="G31" s="36"/>
       <c r="H31" s="27" t="s">
         <v>38</v>
       </c>
     </row>
     <row r="32" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A32" s="35">
+      <c r="A32" s="34">
+        <v>12</v>
+      </c>
+      <c r="B32" s="35" t="s">
+        <v>45</v>
+      </c>
+      <c r="C32" s="36"/>
+      <c r="D32" s="36"/>
+      <c r="E32" s="26"/>
+      <c r="F32" s="36"/>
+      <c r="G32" s="36"/>
+      <c r="H32" s="27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="33" ht="18.5" customHeight="1" spans="1:8">
+      <c r="A33" s="34">
+        <v>13</v>
+      </c>
+      <c r="B33" s="35" t="s">
+        <v>46</v>
+      </c>
+      <c r="C33" s="36"/>
+      <c r="D33" s="36"/>
+      <c r="E33" s="26"/>
+      <c r="F33" s="36"/>
+      <c r="G33" s="36"/>
+      <c r="H33" s="27" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="34" ht="18.5" customHeight="1" spans="1:8">
+      <c r="A34" s="37">
         <v>14</v>
       </c>
-      <c r="B32" s="36" t="s">
+      <c r="B34" s="38" t="s">
         <v>47</v>
       </c>
-      <c r="C32" s="37"/>
-      <c r="D32" s="37"/>
-      <c r="E32" s="38"/>
-      <c r="F32" s="37"/>
-      <c r="G32" s="37"/>
-      <c r="H32" s="39" t="s">
+      <c r="C34" s="39"/>
+      <c r="D34" s="39"/>
+      <c r="E34" s="40"/>
+      <c r="F34" s="39"/>
+      <c r="G34" s="39"/>
+      <c r="H34" s="41" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="33" ht="18.5" customHeight="1" spans="1:8">
-      <c r="A33" s="35">
+    <row r="35" ht="18.5" customHeight="1" spans="1:8">
+      <c r="A35" s="37">
         <v>15</v>
       </c>
-      <c r="B33" s="36" t="s">
+      <c r="B35" s="42" t="s">
         <v>48</v>
       </c>
-      <c r="C33" s="37"/>
-      <c r="D33" s="37"/>
-      <c r="E33" s="40"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="42"/>
+      <c r="C35" s="43"/>
+      <c r="D35" s="43"/>
+      <c r="E35" s="44"/>
+      <c r="F35" s="45"/>
+      <c r="G35" s="45"/>
+      <c r="H35" s="46"/>
     </row>
   </sheetData>
-  <mergeCells count="55">
+  <mergeCells count="57">
     <mergeCell ref="A1:H1"/>
     <mergeCell ref="A2:H2"/>
     <mergeCell ref="A3:H3"/>
@@ -2187,12 +2268,10 @@
     <mergeCell ref="B13:C13"/>
     <mergeCell ref="B14:C14"/>
     <mergeCell ref="B15:C15"/>
-    <mergeCell ref="A16:G16"/>
-    <mergeCell ref="A17:H17"/>
-    <mergeCell ref="B18:D18"/>
-    <mergeCell ref="E18:G18"/>
-    <mergeCell ref="B19:D19"/>
-    <mergeCell ref="E19:G19"/>
+    <mergeCell ref="B16:C16"/>
+    <mergeCell ref="B17:C17"/>
+    <mergeCell ref="A18:G18"/>
+    <mergeCell ref="A19:H19"/>
     <mergeCell ref="B20:D20"/>
     <mergeCell ref="E20:G20"/>
     <mergeCell ref="B21:D21"/>
@@ -2220,9 +2299,16 @@
     <mergeCell ref="B32:D32"/>
     <mergeCell ref="E32:G32"/>
     <mergeCell ref="B33:D33"/>
-    <mergeCell ref="E33:H33"/>
+    <mergeCell ref="E33:G33"/>
+    <mergeCell ref="B34:D34"/>
+    <mergeCell ref="E34:G34"/>
+    <mergeCell ref="B35:D35"/>
+    <mergeCell ref="E35:H35"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
+  <ignoredErrors>
+    <ignoredError sqref="A1:H12 A13:G18 A19:H20 A21:G24 A25:H35" evalError="1"/>
+  </ignoredErrors>
 </worksheet>
 </file>